--- a/data/Non_FI_data.xlsx
+++ b/data/Non_FI_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,121 +413,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W468"/>
+  <dimension ref="A1:W470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Payment Mode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TAT</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Supported Modes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Network participant</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Channels</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Routing code</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Cutoff &amp; delivery timing</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Mandatory data requirements</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Supporting documents</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Beneficiary statement narrative</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Proof of payment</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Beneficiary account type</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - B2B - Max</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - B2B - Min</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - B2P - Max</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - B2P - Min</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - P2B - Max</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - P2B - Min</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - P2P - Max</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Transaction limit per end-user - P2P - Min</t>
         </is>
@@ -553,7 +541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -670,7 +658,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -787,7 +775,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -904,7 +892,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa Direct · ALL</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1001,7 +989,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,7 +1106,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa Direct · DZD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,7 +1203,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1328,7 +1316,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1445,7 +1433,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1562,7 +1550,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1679,7 +1667,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1776,7 +1764,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1893,7 +1881,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Visa Direct · AOA</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1990,7 +1978,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2107,7 +2095,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2224,7 +2212,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2341,7 +2329,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · ARS</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2446,7 +2434,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2563,7 +2551,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2680,7 +2668,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Direct · AMD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2777,7 +2765,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2894,7 +2882,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · AUD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3003,7 +2991,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bank proxy · AUD</t>
+          <t>Bank proxy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3112,7 +3100,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3229,7 +3217,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3346,7 +3334,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3463,7 +3451,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3560,7 +3548,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3677,7 +3665,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa Direct · AZN</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3774,7 +3762,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3891,7 +3879,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa Direct · BSD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3988,7 +3976,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4105,7 +4093,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa Direct · BHD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4202,7 +4190,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GBP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4315,7 +4303,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4432,7 +4420,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4549,7 +4537,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · BDT</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4634,7 +4622,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4751,7 +4739,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa Direct · BDT</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4848,7 +4836,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wallet · BDT</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4937,7 +4925,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5054,7 +5042,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5171,7 +5159,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5288,7 +5276,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5385,7 +5373,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5502,7 +5490,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5619,7 +5607,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Local wire transfer · XOF</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5736,7 +5724,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Visa Direct · XOF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5833,7 +5821,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5950,7 +5938,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa Direct · BMD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6047,7 +6035,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6164,7 +6152,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · BOB</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6277,7 +6265,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6394,7 +6382,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6511,7 +6499,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6628,7 +6616,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6745,7 +6733,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Visa Direct · BWP</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6842,7 +6830,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6959,7 +6947,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · BRL</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7072,7 +7060,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7189,7 +7177,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Proxy payout · BRL</t>
+          <t>Proxy payout</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7290,7 +7278,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7407,7 +7395,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7524,7 +7512,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Visa Direct · BND</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7621,7 +7609,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7738,7 +7726,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7855,7 +7843,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa Direct · BGN</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7952,7 +7940,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8069,7 +8057,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Local wire transfer · XOF</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8186,7 +8174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa Direct · XOF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8283,7 +8271,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8400,7 +8388,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8517,7 +8505,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Visa Direct · KHR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8614,7 +8602,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8731,7 +8719,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Local wire transfer · XAF</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8848,7 +8836,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · CAD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8961,7 +8949,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9074,7 +9062,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9191,7 +9179,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Interac proxy · CAD</t>
+          <t>Interac</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9219,7 +9207,11 @@
           <t>All Interac supported banks in Canada</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TRANSIT NUMBER</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>Near real time(upto 60 mins) - subject to window of 05:00hrs ET to 22:30hrs ET</t>
@@ -9227,7 +9219,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Proxy Type, Proxy Value; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Other: Proxy Type, Proxy Value</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Bank Code/SWIFT Code, Routing Code Type 1 - Transit Code, Routing Code Value 1; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Bank Code/SWIFT Code; Routing: Routing Code Type 1 - Transit Code, Routing Code Value 1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9248,7 +9240,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Beneficiary account should be enabled with auto-deposit to receive payments via interac proxy.</t>
+          <t>Clients wanting to do payment via INTERAC should reach out to their NIUM representative To pass Payout Rail as - "ca_interac" in the payment request</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9300,7 +9292,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Interac · CAD</t>
+          <t>Interac proxy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9328,11 +9320,7 @@
           <t>All Interac supported banks in Canada</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>TRANSIT NUMBER</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Near real time(upto 60 mins) - subject to window of 05:00hrs ET to 22:30hrs ET</t>
@@ -9340,7 +9328,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Bank Code/SWIFT Code, Routing Code Type 1 - Transit Code, Routing Code Value 1; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Bank Code/SWIFT Code; Routing: Routing Code Type 1 - Transit Code, Routing Code Value 1</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Proxy Type, Proxy Value; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remitter City, Remitter Post Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Other: Proxy Type, Proxy Value</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -9361,7 +9349,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Clients wanting to do payment via INTERAC should reach out to their NIUM representative To pass Payout Rail as - "ca_interac" in the payment request</t>
+          <t>Beneficiary account should be enabled with auto-deposit to receive payments via interac proxy.</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9413,7 +9401,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9530,7 +9518,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Visa Direct · CVE</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9627,7 +9615,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9744,7 +9732,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9861,7 +9849,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · CLP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9970,7 +9958,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -10087,7 +10075,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · CNY</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10184,7 +10172,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10301,7 +10289,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Local wire transfer · CNY</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10418,7 +10406,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UnionPay · CNY</t>
+          <t>UnionPay</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10511,7 +10499,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Visa Direct · CNY</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10608,7 +10596,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wallet · CNY</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10693,7 +10681,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10810,7 +10798,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10927,7 +10915,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · COP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -11036,7 +11024,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bre-B proxy · COP</t>
+          <t>Bre-B proxy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11145,7 +11133,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11262,7 +11250,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11379,7 +11367,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Visa Direct · KMF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -11476,7 +11464,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11593,7 +11581,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · CRC</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11686,7 +11674,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11803,7 +11791,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11920,7 +11908,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12037,7 +12025,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12134,7 +12122,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12251,7 +12239,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12368,7 +12356,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12485,7 +12473,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12582,7 +12570,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · CZK</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12691,7 +12679,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12808,7 +12796,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12925,7 +12913,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Visa Direct · CZK</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -13022,7 +13010,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -13139,7 +13127,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · DKK</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13248,7 +13236,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -13365,7 +13353,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13482,7 +13470,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13599,7 +13587,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13716,7 +13704,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Visa Direct · DJF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13813,7 +13801,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13930,7 +13918,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Visa Direct · XCD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -14027,7 +14015,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · DOP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14140,7 +14128,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14257,7 +14245,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Visa Direct · DOP</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14354,7 +14342,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14467,7 +14455,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14584,7 +14572,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · EGP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14669,7 +14657,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14786,7 +14774,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Local wire transfer · EGP</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14903,7 +14891,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Visa Direct · EGP</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -15000,7 +14988,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wallet · EGP</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15085,7 +15073,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15202,7 +15190,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15319,7 +15307,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Visa Direct · XAF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15416,7 +15404,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15533,7 +15521,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15650,7 +15638,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15767,7 +15755,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15864,7 +15852,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15981,7 +15969,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -16098,7 +16086,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Visa Direct · FJD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -16195,7 +16183,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -16312,7 +16300,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -16429,7 +16417,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -16546,7 +16534,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -16663,7 +16651,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -16780,7 +16768,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -16897,7 +16885,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -17014,7 +17002,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -17131,7 +17119,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -17248,7 +17236,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -17365,7 +17353,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Visa Direct · GEL</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -17462,7 +17450,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -17579,7 +17567,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -17696,7 +17684,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -17793,7 +17781,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GHS</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -17906,7 +17894,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -18023,7 +18011,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Visa Direct · GHS</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -18120,7 +18108,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Wallet · GHS</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -18213,7 +18201,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GBP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -18326,7 +18314,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -18443,7 +18431,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -18560,7 +18548,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -18677,7 +18665,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -18794,7 +18782,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -18891,7 +18879,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -19008,7 +18996,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -19125,7 +19113,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -19242,7 +19230,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -19359,7 +19347,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -19472,7 +19460,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -19589,7 +19577,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Visa Direct · USD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -19686,7 +19674,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GTQ</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -19799,7 +19787,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -19916,7 +19904,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Visa Direct · GTQ</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -20013,7 +20001,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GNF</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -20126,7 +20114,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -20243,7 +20231,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -20360,7 +20348,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -20477,7 +20465,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -20594,7 +20582,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Visa Direct · HNL</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -20691,7 +20679,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · HKD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -20804,7 +20792,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -20913,7 +20901,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Faster Payments proxy · HKD</t>
+          <t>Faster Payments proxy</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -21022,12 +21010,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -21047,7 +21035,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>All SWIFT enabled banks in the country</t>
+          <t>All major banks enabled with SWIFT.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -21062,7 +21050,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Routing Code Type 1- SWIFT CODE, Routing Code Value; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Routing: Routing Code Type 1- SWIFT CODE, Routing Code Value</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -21087,7 +21075,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+          <t>Additional documentation may be requested by beneficiary bank to validate underlying transaction and receive credit into account. For WIRES, NIUM supports transactions with SHA Fee Type.</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -21139,12 +21127,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · CNY</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -21164,7 +21152,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>All major banks enabled with SWIFT.</t>
+          <t>All SWIFT enabled banks in the country</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -21179,7 +21167,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Routing Code Type 1- SWIFT CODE, Routing Code Value; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Routing: Routing Code Type 1- SWIFT CODE, Routing Code Value</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -21204,7 +21192,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Additional documentation may be requested by beneficiary bank to validate underlying transaction and receive credit into account. For WIRES, NIUM supports transactions with SHA Fee Type.</t>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -21256,7 +21244,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · HUF</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -21369,7 +21357,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -21486,7 +21474,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -21603,7 +21591,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Visa Direct · HUF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -21700,7 +21688,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -21817,7 +21805,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Local wire transfer · ISK</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -21934,7 +21922,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -22051,7 +22039,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · INR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -22168,7 +22156,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -22285,7 +22273,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Local wire transfer · INR</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -22402,7 +22390,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>UPI proxy · INR</t>
+          <t>UPI proxy</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -22499,7 +22487,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Visa Direct · INR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -22596,7 +22584,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BI-FAST proxy · IDR</t>
+          <t>BI-FAST proxy</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -22705,7 +22693,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · IDR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -22818,7 +22806,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -22935,7 +22923,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Visa Direct · IDR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -23032,7 +23020,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Wallet · IDR</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -23125,7 +23113,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -23242,7 +23230,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -23359,7 +23347,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GBP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -23472,7 +23460,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -23589,7 +23577,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -23706,7 +23694,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · ILS</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -23819,7 +23807,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -23936,7 +23924,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Visa Direct · ILS</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -24033,7 +24021,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -24150,7 +24138,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -24267,7 +24255,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -24364,7 +24352,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · XOF</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -24477,7 +24465,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -24594,7 +24582,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Local wire transfer · XOF</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -24711,7 +24699,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Wallet · XOF</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -24804,7 +24792,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -24921,7 +24909,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Local wire transfer · JMD</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -25038,7 +25026,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · JPY</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -25151,7 +25139,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -25268,7 +25256,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GBP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -25381,7 +25369,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -25498,7 +25486,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -25615,7 +25603,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · JOD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -25720,7 +25708,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -25837,7 +25825,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Visa Direct · JOD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -25934,7 +25922,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -26051,7 +26039,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · KES</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -26164,7 +26152,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -26281,7 +26269,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Visa Direct · KES</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -26378,7 +26366,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Wallet · KES</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -26471,7 +26459,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -26588,7 +26576,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -26705,7 +26693,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -26802,7 +26790,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -26919,7 +26907,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Local wire transfer · KWD</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -27036,7 +27024,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Visa Direct · KWD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -27133,7 +27121,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -27250,7 +27238,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Visa Direct · KGS</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -27347,7 +27335,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -27464,7 +27452,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -27581,7 +27569,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -27698,7 +27686,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -27795,7 +27783,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -27912,7 +27900,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -28029,7 +28017,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -28146,7 +28134,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -28263,7 +28251,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -28380,7 +28368,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -28497,7 +28485,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -28594,7 +28582,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -28711,7 +28699,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -28828,7 +28816,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -28945,7 +28933,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Visa Direct · MOP</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -29042,7 +29030,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -29159,7 +29147,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -29276,7 +29264,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Visa Direct · MKD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -29373,7 +29361,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -29490,7 +29478,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Visa Direct · MGA</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -29587,7 +29575,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -29704,7 +29692,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · MYR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -29821,7 +29809,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DuitNow proxy · MYR</t>
+          <t>DuitNow proxy</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -29930,7 +29918,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -30047,7 +30035,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Visa Direct · MYR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -30144,7 +30132,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -30261,7 +30249,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Visa Direct · MVR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -30358,7 +30346,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -30475,7 +30463,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -30592,7 +30580,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -30689,7 +30677,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -30806,7 +30794,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -30923,7 +30911,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -31040,7 +31028,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -31157,7 +31145,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -31274,7 +31262,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -31391,7 +31379,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · MXN</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -31500,7 +31488,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -31617,7 +31605,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -31734,7 +31722,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -31851,7 +31839,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -31968,7 +31956,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Visa Direct · MDL</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -32065,7 +32053,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -32182,7 +32170,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -32299,7 +32287,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -32416,7 +32404,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Visa Direct · MNT</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -32513,7 +32501,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -32630,7 +32618,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -32747,7 +32735,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -32844,7 +32832,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -32961,7 +32949,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · MAD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -33066,7 +33054,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -33183,7 +33171,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Visa Direct · MAD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -33280,7 +33268,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -33397,7 +33385,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Visa Direct · MZN</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -33494,7 +33482,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -33611,7 +33599,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -33708,7 +33696,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -33825,7 +33813,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · NPR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -33938,7 +33926,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -34055,7 +34043,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Wallet · NPR</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -34148,7 +34136,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -34265,7 +34253,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -34382,7 +34370,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -34479,7 +34467,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -34596,7 +34584,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · NZD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -34705,7 +34693,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -34822,7 +34810,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -34939,7 +34927,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -35056,7 +35044,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · NGN</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -35173,7 +35161,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -35290,7 +35278,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -35407,7 +35395,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -35524,7 +35512,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -35637,7 +35625,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -35754,7 +35742,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · NOK</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -35867,7 +35855,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -35984,7 +35972,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -36101,7 +36089,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -36218,7 +36206,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Visa Direct · OMR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -36315,7 +36303,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · PKR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -36412,7 +36400,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -36529,7 +36517,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Local wire transfer · PKR</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -36646,7 +36634,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Wallet · PKR</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -36723,7 +36711,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -36840,7 +36828,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -36957,7 +36945,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -37074,7 +37062,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -37191,7 +37179,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Visa Direct · PGK</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -37288,7 +37276,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -37405,7 +37393,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · PEN</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -37518,7 +37506,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -37635,7 +37623,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · PHP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -37748,7 +37736,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Cash payout · PHP</t>
+          <t>Cash payout</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -37841,7 +37829,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -37958,7 +37946,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Visa Direct · PHP</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -38055,7 +38043,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Wallet · PHP</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -38148,7 +38136,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -38265,7 +38253,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · PLN</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -38370,7 +38358,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -38487,7 +38475,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -38604,7 +38592,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Visa Direct · PLN</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -38701,7 +38689,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -38818,7 +38806,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -38935,7 +38923,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -39032,7 +39020,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -39145,7 +39133,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 9 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -39262,7 +39250,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -39359,7 +39347,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -39476,7 +39464,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Visa Direct · QAR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -39573,7 +39561,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -39690,7 +39678,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -39807,7 +39795,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -39924,7 +39912,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · RON</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -40033,7 +40021,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -40150,7 +40138,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -40267,7 +40255,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Visa Direct · RON</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -40364,7 +40352,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -40481,7 +40469,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -40598,7 +40586,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -40715,7 +40703,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -40832,7 +40820,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -40949,7 +40937,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -41066,7 +41054,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -41183,7 +41171,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -41300,7 +41288,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -41397,7 +41385,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -41514,7 +41502,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · SAR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -41599,7 +41587,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -41716,7 +41704,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Local wire transfer · SAR</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -41825,7 +41813,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · XOF</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -41938,7 +41926,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -42055,7 +42043,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Local wire transfer · XOF</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -42172,7 +42160,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Wallet · XOF</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -42265,7 +42253,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -42382,7 +42370,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -42499,7 +42487,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Visa Direct · RSD</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -42596,7 +42584,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -42713,7 +42701,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -42830,7 +42818,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · SGD</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -42939,7 +42927,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Bank proxy · SGD</t>
+          <t>Bank proxy</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -43048,12 +43036,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -43073,7 +43061,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>All SWIFT enabled banks in the country</t>
+          <t>All major banks enabled with SWIFT.</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -43088,7 +43076,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Routing Code Type 1- SWIFT CODE, Routing Code Value; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Routing: Routing Code Type 1- SWIFT CODE, Routing Code Value</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -43113,7 +43101,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+          <t>Additional documentation may be requested by beneficiary bank to validate underlying transaction and receive credit into account. For WIRES, NIUM supports transactions with SHA Fee Type.</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -43165,12 +43153,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · CNY</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -43190,7 +43178,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>All major banks enabled with SWIFT.</t>
+          <t>All SWIFT enabled banks in the country</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -43205,7 +43193,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Routing Code Type 1- SWIFT CODE, Routing Code Value; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Routing: Routing Code Type 1- SWIFT CODE, Routing Code Value</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -43230,7 +43218,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>Additional documentation may be requested by beneficiary bank to validate underlying transaction and receive credit into account. For WIRES, NIUM supports transactions with SHA Fee Type.</t>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
         </is>
       </c>
       <c r="P386" t="inlineStr">
@@ -43282,7 +43270,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -43399,7 +43387,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -43516,7 +43504,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -43633,7 +43621,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -43730,7 +43718,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -43847,7 +43835,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -43964,7 +43952,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -44061,7 +44049,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -44178,7 +44166,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · ZAR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -44295,7 +44283,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -44412,7 +44400,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Local wire transfer · ZAR</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -44529,7 +44517,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -44646,7 +44634,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · KRW</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -44759,7 +44747,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -44876,7 +44864,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -44993,7 +44981,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -45110,7 +45098,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Visa Direct · EUR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -45207,7 +45195,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · LKR</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -45316,7 +45304,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -45433,7 +45421,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Visa Direct · LKR</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -45530,7 +45518,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -45647,7 +45635,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -45764,7 +45752,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -45881,7 +45869,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · SEK</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -45990,7 +45978,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -46107,7 +46095,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -46224,7 +46212,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -46341,7 +46329,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -46458,7 +46446,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -46575,7 +46563,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -46692,7 +46680,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Visa Direct · TJS</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -46789,7 +46777,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · TZS</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -46902,7 +46890,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -47019,7 +47007,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Local wire transfer · TZS</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -47136,7 +47124,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Wallet · TZS</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -47233,7 +47221,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · THB</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -47346,7 +47334,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -47463,7 +47451,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Visa Direct · THB</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -47560,7 +47548,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -47677,7 +47665,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Local wire transfer · XOF</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -47794,7 +47782,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Visa Direct · XOF</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -47891,7 +47879,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -48008,7 +47996,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -48125,7 +48113,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Visa Direct · TOP</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -48222,7 +48210,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -48339,7 +48327,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -48456,7 +48444,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · TRY</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -48565,7 +48553,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -48682,7 +48670,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Visa Direct · TRY</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -48779,7 +48767,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -48896,7 +48884,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Visa Direct · TMT</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -48993,7 +48981,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -49110,7 +49098,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -49227,7 +49215,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · UGX</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -49336,7 +49324,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -49453,7 +49441,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Wallet · UGX</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -49546,7 +49534,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -49663,7 +49651,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · AED</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -49772,7 +49760,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -49889,7 +49877,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Local wire transfer · AED</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -49998,7 +49986,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Visa Direct · AED</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -50095,7 +50083,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · GBP</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -50208,7 +50196,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -50325,7 +50313,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -50442,7 +50430,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -50554,17 +50542,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · UYU</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>UYU</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -50579,27 +50567,27 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>All banks in Uruguay</t>
+          <t>All banks in USA in the ACH network</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>BRANCH CODE</t>
+          <t>ACH CODE</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>Same day credit subject to cutoff of 15:00 BRT</t>
+          <t>Same-day day credit subject to cutoff of 15.00 EST</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Address, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Country Code, Beneficiary Account Number, Beneficiary Identification Type, Beneficiary Account Type, Beneficiary Bank Account Type, Beneficiary Identification Value, Routing Code Type 2 - BRANCH CODE, Routing Code Value 2, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1; Remitter: Remitter Name, Remitter Identification Type, Remitter Address, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Country Code, Beneficiary Account Number, Beneficiary Identification Type, Beneficiary Account Type, Beneficiary Bank Account Type, Beneficiary Identification Value; Routing: Routing Code Type 2 - BRANCH CODE, Routing Code Value 2, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1</t>
+          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remitter City, Remitter Address, Remitter State, Remitter Post Code, Remitter Date of Birth (for Individual), Remit Purpose Code, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Name, Beneficiary Address, Beneficiary City, Beneficiary Country Code, Beneficiary Post Code, Beneficiary State, Routing Code Type 1(ACH Code), Routing Code Value 1; Remitter: Remitter Name, Remitter Identification Type, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remitter City, Remitter Address, Remitter State, Remitter Post Code, Remitter Date of Birth (for Individual), Remit Purpose Code; Beneficiary: Beneficiary Account Number, Beneficiary Account Type, Beneficiary Name, Beneficiary Address, Beneficiary City, Beneficiary Country Code, Beneficiary Post Code, Beneficiary State; Routing: Routing Code Type 1(ACH Code), Routing Code Value 1</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
@@ -50609,7 +50597,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>Domestic Clearing System limits ability to transfer full remitter information to the Beneficiary. Visibility of Standard Statement Narration is missing.</t>
+          <t>NIUM Transaction ID is passed on and will be visible in the Beneficiary’s Statement.Remitter Name and statement narrative will be visible in the Beneficiary’s Account Statement. Clearing system can limit value of each field visible upto 10 characters.</t>
         </is>
       </c>
       <c r="M452" t="inlineStr"/>
@@ -50618,10 +50606,14 @@
           <t>CORPORATE</t>
         </is>
       </c>
-      <c r="O452" t="inlineStr"/>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>USD ACH payouts can also be done to below countries if the ACH code is supported as  per regulator guidelines.  - U. S. Virgin Islands , Guam  American Samoa , The Northern Mariana Islands.The status update will be done on end of day basis though the Beneficiary may receive the  credit before this.</t>
+        </is>
+      </c>
       <c r="P452" t="inlineStr">
         <is>
-          <t>UYU 5,000,000</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="Q452" t="inlineStr">
@@ -50631,7 +50623,7 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>UYU 5,000,000</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="S452" t="inlineStr">
@@ -50641,7 +50633,7 @@
       </c>
       <c r="T452" t="inlineStr">
         <is>
-          <t>UYU 5,000,000</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="U452" t="inlineStr">
@@ -50651,7 +50643,7 @@
       </c>
       <c r="V452" t="inlineStr">
         <is>
-          <t>UYU 5,000,000</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="W452" t="inlineStr">
@@ -50663,12 +50655,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -50780,22 +50772,22 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>UYU</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>SAME DAY</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -50805,27 +50797,27 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>All SWIFT enabled banks in the country</t>
+          <t>All banks in Uruguay</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>BRANCH CODE</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+          <t>Same day credit subject to cutoff of 15:00 BRT</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Address, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Country Code, Beneficiary Account Number, Beneficiary Identification Type, Beneficiary Account Type, Beneficiary Bank Account Type, Beneficiary Identification Value, Routing Code Type 2 - BRANCH CODE, Routing Code Value 2, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1; Remitter: Remitter Name, Remitter Identification Type, Remitter Address, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Country Code, Beneficiary Account Number, Beneficiary Identification Type, Beneficiary Account Type, Beneficiary Bank Account Type, Beneficiary Identification Value; Routing: Routing Code Type 2 - BRANCH CODE, Routing Code Value 2, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
@@ -50835,27 +50827,19 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
-        </is>
-      </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
-        </is>
-      </c>
+          <t>Domestic Clearing System limits ability to transfer full remitter information to the Beneficiary. Visibility of Standard Statement Narration is missing.</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr"/>
       <c r="N454" t="inlineStr">
         <is>
           <t>CORPORATE</t>
         </is>
       </c>
-      <c r="O454" t="inlineStr">
-        <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
-        </is>
-      </c>
+      <c r="O454" t="inlineStr"/>
       <c r="P454" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>UYU 5,000,000</t>
         </is>
       </c>
       <c r="Q454" t="inlineStr">
@@ -50865,7 +50849,7 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>UYU 5,000,000</t>
         </is>
       </c>
       <c r="S454" t="inlineStr">
@@ -50875,7 +50859,7 @@
       </c>
       <c r="T454" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>UYU 5,000,000</t>
         </is>
       </c>
       <c r="U454" t="inlineStr">
@@ -50885,7 +50869,7 @@
       </c>
       <c r="V454" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>UYU 5,000,000</t>
         </is>
       </c>
       <c r="W454" t="inlineStr">
@@ -50897,22 +50881,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Visa Direct · UZS</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -50922,24 +50906,44 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>VISA</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>All SWIFT enabled banks in the country</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>SWIFT</t>
+        </is>
+      </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>1. 24x7 Availability | 2. Real-time for Fast fund Enabled (Details on fast-fund enabled countries available on request) | 3. T+2 for other countries</t>
+          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code, Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code; Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code; Beneficiary: Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code</t>
-        </is>
-      </c>
-      <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr"/>
-      <c r="M455" t="inlineStr"/>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Remitter Beneficiary Relationship, Nature of Business, Duration of Contract, Commercial Agreement, Current Invoice</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+        </is>
+      </c>
       <c r="N455" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -50947,12 +50951,12 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>For more information, please contact your NIUM account manager team. Additional information and approval from VISA is required before this payout method can be made available. Origination of funds is allowed only from a set of countries as mentioned in the table below. In case the transaction currency does not match the destination card issuer currency, amount will be converted and credited in currency of the card issuer. In few countries, only few banks may allow the transactions. Below additional daily/monthly/yearly limits applicable for P2P transactions whichever reached first Per Day - 30 transactions or USD 10,000 per Beneficiary card Per Week - 50 transactions or USD 25,000 per Beneficiary card Per Month - 150 transactions or USD 50,000 per Beneficiary card. Below additional daily/monthly/yearly limits applicable for B2P/B2B transactions whichever reached first Per Day - 30 transactions or USD 50,000 per Beneficiary card Per Week - 50 transactions or USD 100,000 per Beneficiary card Per Month - 150 transactions or USD 200,000 per Beneficiary card.</t>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
         </is>
       </c>
       <c r="P455" t="inlineStr">
         <is>
-          <t>USD 50,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="Q455" t="inlineStr">
@@ -50962,7 +50966,7 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>USD 50,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="S455" t="inlineStr">
@@ -50972,7 +50976,7 @@
       </c>
       <c r="T455" t="inlineStr">
         <is>
-          <t>USD 50,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="U455" t="inlineStr">
@@ -50982,7 +50986,7 @@
       </c>
       <c r="V455" t="inlineStr">
         <is>
-          <t>USD 2,500</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="W455" t="inlineStr">
@@ -50994,12 +50998,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -51111,22 +51115,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Vatican City State</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -51136,44 +51140,24 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>All SWIFT enabled banks in the country</t>
-        </is>
-      </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>SWIFT</t>
-        </is>
-      </c>
+          <t>VISA</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+          <t>1. 24x7 Availability | 2. Real-time for Fast fund Enabled (Details on fast-fund enabled countries available on request) | 3. T+2 for other countries</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
-        </is>
-      </c>
-      <c r="K457" t="inlineStr">
-        <is>
-          <t>Remitter Beneficiary Relationship, Nature of Business, Duration of Contract, Commercial Agreement, Current Invoice</t>
-        </is>
-      </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
-        </is>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
-        </is>
-      </c>
+          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code, Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code; Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code; Beneficiary: Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
       <c r="N457" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -51181,12 +51165,12 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+          <t>For more information, please contact your NIUM account manager team. Additional information and approval from VISA is required before this payout method can be made available. Origination of funds is allowed only from a set of countries as mentioned in the table below. In case the transaction currency does not match the destination card issuer currency, amount will be converted and credited in currency of the card issuer. In few countries, only few banks may allow the transactions. Below additional daily/monthly/yearly limits applicable for P2P transactions whichever reached first Per Day - 30 transactions or USD 10,000 per Beneficiary card Per Week - 50 transactions or USD 25,000 per Beneficiary card Per Month - 150 transactions or USD 50,000 per Beneficiary card. Below additional daily/monthly/yearly limits applicable for B2P/B2B transactions whichever reached first Per Day - 30 transactions or USD 50,000 per Beneficiary card Per Week - 50 transactions or USD 100,000 per Beneficiary card Per Month - 150 transactions or USD 200,000 per Beneficiary card.</t>
         </is>
       </c>
       <c r="P457" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 50,000</t>
         </is>
       </c>
       <c r="Q457" t="inlineStr">
@@ -51196,7 +51180,7 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 50,000</t>
         </is>
       </c>
       <c r="S457" t="inlineStr">
@@ -51206,7 +51190,7 @@
       </c>
       <c r="T457" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 50,000</t>
         </is>
       </c>
       <c r="U457" t="inlineStr">
@@ -51216,7 +51200,7 @@
       </c>
       <c r="V457" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 2,500</t>
         </is>
       </c>
       <c r="W457" t="inlineStr">
@@ -51228,22 +51212,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Vatican City State</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>SEPA · EUR</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>SAME DAY</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -51258,7 +51242,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>All banks connected with SEPA Network</t>
+          <t>All SWIFT enabled banks in the country</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -51268,12 +51252,12 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>1. Real-time for transaction amount &lt;= EUR 100,000 | 2. Same-day for transaction amount &gt; EUR 100,000 subject to cutoff of 14.00 EET</t>
+          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Address, Remitter Country Code, Remitter Identification Type, Remitter Identification Number, Remit Purpose Code, Remitter City, Remitter Postcode, Beneficiary Name, Beneficiary Country Code, Beneficiary Account Type, Beneficiary Account Number - IBAN, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1; Remitter: Remitter Name, Remitter Account Type, Remitter Address, Remitter Country Code, Remitter Identification Type, Remitter Identification Number, Remit Purpose Code, Remitter City, Remitter Postcode; Beneficiary: Beneficiary Name, Beneficiary Country Code, Beneficiary Account Type, Beneficiary Account Number - IBAN; Routing: Routing Code Type 1 - SWIFT CODE, Routing Code Value 1</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
@@ -51283,12 +51267,12 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>Remitter Name &amp; NIUM appears in the beneficiary statement</t>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Upon request, Proof of Payment for a transaction can be made available.</t>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -51298,7 +51282,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>Coverage includes the EU as well as several Non-EU countries. Not all supported countries support  Realtime payments Few banks in Instant supported countries may not support instant payments and payments will be routed through Standard mode in such cases. 4.Certain banks require the complete 11-character SWIFT code—including the branch identifier—in order to accurately route and successfully process the payment.</t>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
         </is>
       </c>
       <c r="P458" t="inlineStr">
@@ -51308,7 +51292,7 @@
       </c>
       <c r="Q458" t="inlineStr">
         <is>
-          <t>EUR 0.01</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
@@ -51318,7 +51302,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>EUR 0.01</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="T458" t="inlineStr">
@@ -51328,7 +51312,7 @@
       </c>
       <c r="U458" t="inlineStr">
         <is>
-          <t>EUR 0.01</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="V458" t="inlineStr">
@@ -51338,29 +51322,29 @@
       </c>
       <c r="W458" t="inlineStr">
         <is>
-          <t>EUR 0.01</t>
+          <t>Not specified</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Vatican City State</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · VND</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>INSTANT</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -51375,18 +51359,22 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>All banks in Vietnam</t>
-        </is>
-      </c>
-      <c r="H459" t="inlineStr"/>
+          <t>All SWIFT enabled banks in the country</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>SWIFT</t>
+        </is>
+      </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>24x7 Availability, Delivery - Real Time for 30+ Major Banks ( List available). | All Other Banks- Delivery - T0, Cut-off - 07:30 GMT</t>
+          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Address, Beneficiary Account Type, Beneficiary Account Number, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Address, Beneficiary Account Type, Beneficiary Account Number; Routing: Routing Code Type 1 - SWIFT CODE, Routing Code Value 1</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -51396,10 +51384,14 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>Remitter Name will be sent to the beneficiary bank and visible in the beneficiary statement. Statement Narrative is also sent to the beneficiary bank but depends on the beneficiary bank to display the information.</t>
-        </is>
-      </c>
-      <c r="M459" t="inlineStr"/>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+        </is>
+      </c>
       <c r="N459" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -51407,69 +51399,69 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>Documents may be asked by  bank for transaction amount  &gt; 250 Mn VND</t>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
         <is>
-          <t>VND 500,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
-          <t>VND 2,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>VND 500,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>VND 2,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="T459" t="inlineStr">
         <is>
-          <t>VND 500,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="U459" t="inlineStr">
         <is>
-          <t>VND 2,000</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="V459" t="inlineStr">
         <is>
-          <t>VND 500,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="W459" t="inlineStr">
         <is>
-          <t>VND 2,000</t>
+          <t>Not specified</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Vatican City State</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>SEPA</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>SAME DAY</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -51484,7 +51476,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>All SWIFT enabled banks in the country</t>
+          <t>All banks connected with SEPA Network</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -51494,12 +51486,12 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+          <t>1. Real-time for transaction amount &lt;= EUR 100,000 | 2. Same-day for transaction amount &gt; EUR 100,000 subject to cutoff of 14.00 EET</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Address, Remitter Country Code, Remitter Identification Type, Remitter Identification Number, Remit Purpose Code, Remitter City, Remitter Postcode, Beneficiary Name, Beneficiary Country Code, Beneficiary Account Type, Beneficiary Account Number - IBAN, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1; Remitter: Remitter Name, Remitter Account Type, Remitter Address, Remitter Country Code, Remitter Identification Type, Remitter Identification Number, Remit Purpose Code, Remitter City, Remitter Postcode; Beneficiary: Beneficiary Name, Beneficiary Country Code, Beneficiary Account Type, Beneficiary Account Number - IBAN; Routing: Routing Code Type 1 - SWIFT CODE, Routing Code Value 1</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
@@ -51509,12 +51501,12 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+          <t>Remitter Name &amp; NIUM appears in the beneficiary statement</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+          <t>Upon request, Proof of Payment for a transaction can be made available.</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -51524,7 +51516,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+          <t>Coverage includes the EU as well as several Non-EU countries. Not all supported countries support  Realtime payments Few banks in Instant supported countries may not support instant payments and payments will be routed through Standard mode in such cases. 4.Certain banks require the complete 11-character SWIFT code—including the branch identifier—in order to accurately route and successfully process the payment.</t>
         </is>
       </c>
       <c r="P460" t="inlineStr">
@@ -51534,7 +51526,7 @@
       </c>
       <c r="Q460" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>EUR 0.01</t>
         </is>
       </c>
       <c r="R460" t="inlineStr">
@@ -51544,7 +51536,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>EUR 0.01</t>
         </is>
       </c>
       <c r="T460" t="inlineStr">
@@ -51554,7 +51546,7 @@
       </c>
       <c r="U460" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>EUR 0.01</t>
         </is>
       </c>
       <c r="V460" t="inlineStr">
@@ -51564,7 +51556,7 @@
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>EUR 0.01</t>
         </is>
       </c>
     </row>
@@ -51576,7 +51568,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Local wire transfer · VND</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -51586,7 +51578,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>INSTANT</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -51601,22 +51593,18 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>All major banks enabled with SWIFT</t>
-        </is>
-      </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>SWIFT</t>
-        </is>
-      </c>
+          <t>All banks in Vietnam</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Same-day processing subject to cutoff of 7:30 UTC</t>
+          <t>24x7 Availability, Delivery - Real Time for 30+ Major Banks ( List available). | All Other Banks- Delivery - T0, Cut-off - 07:30 GMT</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter IDentification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Routing Code Type 1 - SWIFT CODE, Routing Code Value; Remitter: Remitter Name, Remitter Account Type, Remitter IDentification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Routing: Routing Code Type 1 - SWIFT CODE, Routing Code Value</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Address, Beneficiary Account Type, Beneficiary Account Number, Routing Code Type 1 - SWIFT CODE, Routing Code Value 1; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Address, Beneficiary Account Type, Beneficiary Account Number; Routing: Routing Code Type 1 - SWIFT CODE, Routing Code Value 1</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
@@ -51626,14 +51614,10 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
-        </is>
-      </c>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
-        </is>
-      </c>
+          <t>Remitter Name will be sent to the beneficiary bank and visible in the beneficiary statement. Statement Narrative is also sent to the beneficiary bank but depends on the beneficiary bank to display the information.</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr"/>
       <c r="N461" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -51641,47 +51625,47 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>For WIRES, NIUM supports transactions with SHA Fee Type</t>
+          <t>Documents may be asked by  bank for transaction amount  &gt; 250 Mn VND</t>
         </is>
       </c>
       <c r="P461" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>VND 500,000,000</t>
         </is>
       </c>
       <c r="Q461" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>VND 2,000</t>
         </is>
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>VND 500,000,000</t>
         </is>
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>VND 2,000</t>
         </is>
       </c>
       <c r="T461" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>VND 500,000,000</t>
         </is>
       </c>
       <c r="U461" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>VND 2,000</t>
         </is>
       </c>
       <c r="V461" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>VND 500,000,000</t>
         </is>
       </c>
       <c r="W461" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>VND 2,000</t>
         </is>
       </c>
     </row>
@@ -51693,17 +51677,17 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Visa Direct · VND</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>INSTANT</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -51713,24 +51697,44 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>VISA</t>
-        </is>
-      </c>
-      <c r="G462" t="inlineStr"/>
-      <c r="H462" t="inlineStr"/>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>All SWIFT enabled banks in the country</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>SWIFT</t>
+        </is>
+      </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>1. 24x7 Availability | 2. Real-time for Fast fund Enabled (Details on fast-fund enabled countries available on request) | 3. T+2 for other countries</t>
+          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code, Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code; Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code; Beneficiary: Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code</t>
-        </is>
-      </c>
-      <c r="K462" t="inlineStr"/>
-      <c r="L462" t="inlineStr"/>
-      <c r="M462" t="inlineStr"/>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Remitter Beneficiary Relationship, Nature of Business, Duration of Contract, Commercial Agreement, Current Invoice</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+        </is>
+      </c>
       <c r="N462" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -51738,12 +51742,12 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>For more information, please contact your NIUM account manager team. Additional information and approval from VISA is required before this payout method can be made available. Origination of funds is allowed only from a set of countries as mentioned in the table below. In case the transaction currency does not match the destination card issuer currency, amount will be converted and credited in currency of the card issuer. In few countries, only few banks may allow the transactions. Below additional daily/monthly/yearly limits applicable for P2P transactions whichever reached first Per Day - 30 transactions or USD 10,000 per Beneficiary card Per Week - 50 transactions or USD 25,000 per Beneficiary card Per Month - 150 transactions or USD 50,000 per Beneficiary card. Below additional daily/monthly/yearly limits applicable for B2P/B2B transactions whichever reached first Per Day - 30 transactions or USD 50,000 per Beneficiary card Per Week - 50 transactions or USD 100,000 per Beneficiary card Per Month - 150 transactions or USD 200,000 per Beneficiary card.</t>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
         </is>
       </c>
       <c r="P462" t="inlineStr">
         <is>
-          <t>USD 50,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="Q462" t="inlineStr">
@@ -51753,7 +51757,7 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>USD 50,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="S462" t="inlineStr">
@@ -51763,7 +51767,7 @@
       </c>
       <c r="T462" t="inlineStr">
         <is>
-          <t>USD 50,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="U462" t="inlineStr">
@@ -51773,7 +51777,7 @@
       </c>
       <c r="V462" t="inlineStr">
         <is>
-          <t>USD 2,500</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="W462" t="inlineStr">
@@ -51785,22 +51789,22 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Virgin Islands (U.S.)</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Bank account (ACH) · USD</t>
+          <t>Local wire transfer</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>SAME DAY</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -51815,22 +51819,22 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>All banks in USA in the ACH network</t>
+          <t>All major banks enabled with SWIFT</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>ACH CODE</t>
+          <t>SWIFT</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>Same-day day credit subject to cutoff of 15.00 EST</t>
+          <t>Same-day processing subject to cutoff of 7:30 UTC</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remitter City, Remitter Address, Remitter State, Remitter Post Code, Remitter Date of Birth (for Individual), Remit Purpose Code, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Name, Beneficiary Address, Beneficiary City, Beneficiary Country Code, Beneficiary Post Code, Beneficiary State, Routing Code Type 1(ACH Code), Routing Code Value 1; Remitter: Remitter Name, Remitter Identification Type, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remitter City, Remitter Address, Remitter State, Remitter Post Code, Remitter Date of Birth (for Individual), Remit Purpose Code; Beneficiary: Beneficiary Account Number, Beneficiary Account Type, Beneficiary Name, Beneficiary Address, Beneficiary City, Beneficiary Country Code, Beneficiary Post Code, Beneficiary State; Routing: Routing Code Type 1(ACH Code), Routing Code Value 1</t>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter IDentification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Routing Code Type 1 - SWIFT CODE, Routing Code Value; Remitter: Remitter Name, Remitter Account Type, Remitter IDentification Type, Remitter Identification Number, Remitter Address, Remitter Country code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode; Routing: Routing Code Type 1 - SWIFT CODE, Routing Code Value</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -51840,10 +51844,14 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>NIUM Transaction ID is passed on and will be visible in the Beneficiary’s Statement.Remitter Name and statement narrative will be visible in the Beneficiary’s Account Statement. Clearing system can limit value of each field visible upto 10 characters.</t>
-        </is>
-      </c>
-      <c r="M463" t="inlineStr"/>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+        </is>
+      </c>
       <c r="N463" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -51851,12 +51859,12 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>USD ACH payouts can also be done to below countries if the ACH code is supported as  per regulator guidelines.  - U. S. Virgin Islands , Guam  American Samoa , The Northern Mariana Islands.The status update will be done on end of day basis though the Beneficiary may receive the  credit before this.</t>
+          <t>For WIRES, NIUM supports transactions with SHA Fee Type</t>
         </is>
       </c>
       <c r="P463" t="inlineStr">
         <is>
-          <t>USD 1,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="Q463" t="inlineStr">
@@ -51866,7 +51874,7 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>USD 1,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="S463" t="inlineStr">
@@ -51876,7 +51884,7 @@
       </c>
       <c r="T463" t="inlineStr">
         <is>
-          <t>USD 1,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="U463" t="inlineStr">
@@ -51886,7 +51894,7 @@
       </c>
       <c r="V463" t="inlineStr">
         <is>
-          <t>USD 1,000,000</t>
+          <t>No limit</t>
         </is>
       </c>
       <c r="W463" t="inlineStr">
@@ -51898,22 +51906,22 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Virgin Islands (U.S.)</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Visa Direct</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>INSTANT</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -51923,44 +51931,24 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>All SWIFT enabled banks in the country</t>
-        </is>
-      </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>SWIFT</t>
-        </is>
-      </c>
+          <t>VISA</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+          <t>1. 24x7 Availability | 2. Real-time for Fast fund Enabled (Details on fast-fund enabled countries available on request) | 3. T+2 for other countries</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
-        </is>
-      </c>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>Remitter Beneficiary Relationship, Nature of Business, Duration of Contract, Commercial Agreement, Current Invoice</t>
-        </is>
-      </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
-        </is>
-      </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
-        </is>
-      </c>
+          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code, Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code; Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code; Beneficiary: Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
       <c r="N464" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -51968,12 +51956,12 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+          <t>For more information, please contact your NIUM account manager team. Additional information and approval from VISA is required before this payout method can be made available. Origination of funds is allowed only from a set of countries as mentioned in the table below. In case the transaction currency does not match the destination card issuer currency, amount will be converted and credited in currency of the card issuer. In few countries, only few banks may allow the transactions. Below additional daily/monthly/yearly limits applicable for P2P transactions whichever reached first Per Day - 30 transactions or USD 10,000 per Beneficiary card Per Week - 50 transactions or USD 25,000 per Beneficiary card Per Month - 150 transactions or USD 50,000 per Beneficiary card. Below additional daily/monthly/yearly limits applicable for B2P/B2B transactions whichever reached first Per Day - 30 transactions or USD 50,000 per Beneficiary card Per Week - 50 transactions or USD 100,000 per Beneficiary card Per Month - 150 transactions or USD 200,000 per Beneficiary card.</t>
         </is>
       </c>
       <c r="P464" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 50,000</t>
         </is>
       </c>
       <c r="Q464" t="inlineStr">
@@ -51983,7 +51971,7 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 50,000</t>
         </is>
       </c>
       <c r="S464" t="inlineStr">
@@ -51993,7 +51981,7 @@
       </c>
       <c r="T464" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 50,000</t>
         </is>
       </c>
       <c r="U464" t="inlineStr">
@@ -52003,7 +51991,7 @@
       </c>
       <c r="V464" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 2,500</t>
         </is>
       </c>
       <c r="W464" t="inlineStr">
@@ -52015,22 +52003,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Wallis and Futuna Islands</t>
+          <t>Virgin Islands (U.S.)</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Bank account (ACH)</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>SAME DAY</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -52045,22 +52033,22 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>All SWIFT enabled banks in the country</t>
+          <t>All banks in USA in the ACH network</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>ACH CODE</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+          <t>Same-day day credit subject to cutoff of 15.00 EST</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+          <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remitter City, Remitter Address, Remitter State, Remitter Post Code, Remitter Date of Birth (for Individual), Remit Purpose Code, Beneficiary Account Number, Beneficiary Account Type, Beneficiary Name, Beneficiary Address, Beneficiary City, Beneficiary Country Code, Beneficiary Post Code, Beneficiary State, Routing Code Type 1(ACH Code), Routing Code Value 1; Remitter: Remitter Name, Remitter Identification Type, Remitter Account Type, Remitter Identification Number, Remitter Country Code, Remitter City, Remitter Address, Remitter State, Remitter Post Code, Remitter Date of Birth (for Individual), Remit Purpose Code; Beneficiary: Beneficiary Account Number, Beneficiary Account Type, Beneficiary Name, Beneficiary Address, Beneficiary City, Beneficiary Country Code, Beneficiary Post Code, Beneficiary State; Routing: Routing Code Type 1(ACH Code), Routing Code Value 1</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -52070,14 +52058,10 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
-        </is>
-      </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
-        </is>
-      </c>
+          <t>NIUM Transaction ID is passed on and will be visible in the Beneficiary’s Statement.Remitter Name and statement narrative will be visible in the Beneficiary’s Account Statement. Clearing system can limit value of each field visible upto 10 characters.</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr"/>
       <c r="N465" t="inlineStr">
         <is>
           <t>CORPORATE</t>
@@ -52085,12 +52069,12 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+          <t>USD ACH payouts can also be done to below countries if the ACH code is supported as  per regulator guidelines.  - U. S. Virgin Islands , Guam  American Samoa , The Northern Mariana Islands.The status update will be done on end of day basis though the Beneficiary may receive the  credit before this.</t>
         </is>
       </c>
       <c r="P465" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="Q465" t="inlineStr">
@@ -52100,7 +52084,7 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="S465" t="inlineStr">
@@ -52110,7 +52094,7 @@
       </c>
       <c r="T465" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="U465" t="inlineStr">
@@ -52120,7 +52104,7 @@
       </c>
       <c r="V465" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>USD 1,000,000</t>
         </is>
       </c>
       <c r="W465" t="inlineStr">
@@ -52132,12 +52116,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Western Sahara</t>
+          <t>Virgin Islands (U.S.)</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -52249,12 +52233,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Wallis and Futuna Islands</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Foreign currency wire transfer · 10 currencies</t>
+          <t>Foreign currency wire transfer</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -52366,95 +52350,329 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
+          <t>Western Sahara</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Foreign currency wire transfer</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>B2B, B2P, P2P, P2B</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>All SWIFT enabled banks in the country</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>SWIFT</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Remitter Beneficiary Relationship, Nature of Business, Duration of Contract, Commercial Agreement, Current Invoice</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="W468" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Visa Direct · ZMW</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Foreign currency wire transfer</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>USD, EUR, SGD, GBP, AUD, CAD, HKD, JPY, CHF, NZD</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>B2B, B2P, P2P, P2B</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>All SWIFT enabled banks in the country</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>SWIFT</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Same-day processing subject to cutoff of 07:30 UTC</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code, Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended), Routing Code Value 1, Routing Code Type 1 - SWIFT Code; Remitter: Remitter Name, Remitter Account Type, Remitter Identification Type, Remitter Identification Number, Remitter Address, Remitter Country Code, Remit Purpose Code; Beneficiary: Beneficiary Name, Beneficiary Account Type, Beneficiary Account Number, Beneficiary Country Code, Beneficiary Address, Beneficiary City, Beneficiary Postcode, Beneficiary Address (Recommended), Beneficiary City (Recommended), Beneficiary Postcode (Recommended); Routing: Routing Code Value 1, Routing Code Type 1 - SWIFT Code</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Remitter Beneficiary Relationship, Nature of Business, Duration of Contract, Commercial Agreement, Current Invoice</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Ultimate Sender Name and narrative details will be passed as part of pacs.008 message to beneficiary bank. Details available on beneficiary statement will be dependent on beneficiary bank.</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>pacs.008 can be considered as a proof of payment and can be provided on request</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>WIRES can be sent to all countries except for OFAC listed. pacs.008 can be provided on request. NIUM does not support OUR charge type for CAD currency WIRES Processing of payments to Crimea, Donetsk, Luhansk, Sevastopol regions of Ukraine is prohibited. This list is subject to change. For foreign currency wire currencies USD, EUR, GBP - NIUM supports both OUR and SHA fee type while for other currencies AUD, CAD, CHF, JPY, NZD, HKD, SGD - NIUM supports only SHA fee type</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="W469" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Visa Direct</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
         <is>
           <t>ZMW</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
+      <c r="D470" t="inlineStr">
         <is>
           <t>INSTANT</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr">
+      <c r="E470" t="inlineStr">
         <is>
           <t>B2B, B2P, P2P, P2B</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr">
+      <c r="F470" t="inlineStr">
         <is>
           <t>VISA</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr"/>
-      <c r="I468" t="inlineStr">
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
         <is>
           <t>1. 24x7 Availability | 2. Real-time for Fast fund Enabled (Details on fast-fund enabled countries available on request) | 3. T+2 for other countries</t>
         </is>
       </c>
-      <c r="J468" t="inlineStr">
+      <c r="J470" t="inlineStr">
         <is>
           <t>Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code, Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code; Remitter: Remitter Name, Remitter Identification Type, Remitter Identification Number, Remitter Country Code; Beneficiary: Beneficiary Card Number, Beneficiary Name, Beneficiary Country Code</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
-      <c r="L468" t="inlineStr"/>
-      <c r="M468" t="inlineStr"/>
-      <c r="N468" t="inlineStr">
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
+      <c r="N470" t="inlineStr">
         <is>
           <t>CORPORATE</t>
         </is>
       </c>
-      <c r="O468" t="inlineStr">
+      <c r="O470" t="inlineStr">
         <is>
           <t>For more information, please contact your NIUM account manager team. Additional information and approval from VISA is required before this payout method can be made available. Origination of funds is allowed only from a set of countries as mentioned in the table below. In case the transaction currency does not match the destination card issuer currency, amount will be converted and credited in currency of the card issuer. In few countries, only few banks may allow the transactions. Below additional daily/monthly/yearly limits applicable for P2P transactions whichever reached first Per Day - 30 transactions or USD 10,000 per Beneficiary card Per Week - 50 transactions or USD 25,000 per Beneficiary card Per Month - 150 transactions or USD 50,000 per Beneficiary card. Below additional daily/monthly/yearly limits applicable for B2P/B2B transactions whichever reached first Per Day - 30 transactions or USD 50,000 per Beneficiary card Per Week - 50 transactions or USD 100,000 per Beneficiary card Per Month - 150 transactions or USD 200,000 per Beneficiary card.</t>
         </is>
       </c>
-      <c r="P468" t="inlineStr">
+      <c r="P470" t="inlineStr">
         <is>
           <t>USD 50,000</t>
         </is>
       </c>
-      <c r="Q468" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R468" t="inlineStr">
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
         <is>
           <t>USD 50,000</t>
         </is>
       </c>
-      <c r="S468" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="T468" t="inlineStr">
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
         <is>
           <t>USD 50,000</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V468" t="inlineStr">
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
         <is>
           <t>USD 2,500</t>
         </is>
       </c>
-      <c r="W468" t="inlineStr">
+      <c r="W470" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
